--- a/templates/modelo-carga-vendas-vendedor.xlsx
+++ b/templates/modelo-carga-vendas-vendedor.xlsx
@@ -921,7 +921,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>MB (%)      -&gt; NÃO vai na planilha: o sistema calcula MP / RL.</t>
+          <t>MC1%      -&gt; NÃO vai na planilha: o sistema calcula MP / RL.</t>
         </is>
       </c>
     </row>
